--- a/spreadsheets/science.xlsx
+++ b/spreadsheets/science.xlsx
@@ -43,40 +43,40 @@
     <t xml:space="preserve">(2025) Journal of Royal Statistical Society Series A: Statistics in Society</t>
   </si>
   <si>
+    <t xml:space="preserve">Immediately following a disaster event, such as an earthquake, estimates of the damage extent play a key role in informing the coordination of response and recovery efforts. We develop a novel impact estimation tool that leverages a generalised Bayesian approach to generate earthquake impact estimates across three impact types: mortality, population displacement, and building damage. Inference is performed within a likelihood-free framework, and a scoring-rule-based posterior avoids information loss from non-sufficient summary statistics. We propose an adaptation of existing scoring-rule-based loss functions that accommodates the use of an approximate Bayesian computation sequential Monte Carlo (ABC-SMC) framework. The fitted model achieves results comparable to those of two leading impact estimation tools in the prediction of total mortality when tested on a set of held-out past events. The proposed method provides four advantages over existing empirical approaches: modelling produces a gridded spatial map of the estimated impact, predictions benefit from the Bayesian quantification and interpretation of uncertainty, there is direct handling of multi-shock earthquake events, and the use of a joint model between impact types allows predictions to be updated as impact observations become available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://arxiv.org/abs/2412.15791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Images/Science/oddrin.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disasters, Statistics and the Humanitarian Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2026) Annals of Statistics and their </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This article examines the role of statistics in the humanitarian sector, with a particular focus on disasters caused by natural hazards. It begins by outlining current applications, including primary data collection, anticipatory action frameworks, Earth observation, mobile positioning data, and artificial intelligence. It then highlights key challenges such as gaps and biases in disaster impact and response data, difficulties in communicating statistical findings clearly, inequities in aid allocation, and the widespread outsourcing of statistics-related work. In exploring future applications, the article discusses the potential of impact-based early warning models, dynamic population data, and artificial intelligence to enhance communication and decision-making. Throughout, emphasis is placed on the need for interoperable systems as well as ethical and inclusive data practices. In doing so, the article presents statistics as both a diagnostic and strategic tool for strengthening the effectiveness, fairness, and responsiveness of humanitarian action in disaster contexts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.annualreviews.org/content/journals/10.1146/annurev-statistics-042424-061122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Images/Science/arsia.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayesian spatiotemporal modelling of political violence and conflict events using discrete-time Hawkes processes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2026) Journal of Royal Statistical Society Series A: Statistics in Society</t>
+  </si>
+  <si>
     <t xml:space="preserve">The monitoring of conflict risk in the humanitarian sector is largely based on simple historic averages. The overarching goal of this work is to assess the potential for using a more statistically rigorous approach to monitor the risk of political violence and conflict events in practice, and thereby improve our understanding of their temporal and spatial patterns, to inform preventative measures. In particular, a Bayesian, spatiotemporal variant of the Hawkes process is fitted to data gathered by the Armed Conflict Location and Event Data (ACLED) project to obtain sub-national estimates of conflict risk in South Asia over time and space. Our model can effectively estimate the risk level of these events within a statistically sound framework, with a more precise understanding of uncertainty than was previously possible. The model also provides insights into differences in behaviours between countries and conflict types. We also show how our model can be used to monitor short and long term trends, and that it is more stable and robust to outliers compared to current practices that rely on historical averages.</t>
   </si>
   <si>
     <t xml:space="preserve">https://academic.oup.com/jrsssa/advance-article/doi/10.1093/jrsssa/qnag039/8539545?guestAccessKey=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Science/oddrin.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disasters, Statistics and the Humanitarian Sector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2026) Annals of Statistics and their </t>
-  </si>
-  <si>
-    <t xml:space="preserve">This article examines the role of statistics in the humanitarian sector, with a particular focus on disasters caused by natural hazards. It begins by outlining current applications, including primary data collection, anticipatory action frameworks, Earth observation, mobile positioning data, and artificial intelligence. It then highlights key challenges such as gaps and biases in disaster impact and response data, difficulties in communicating statistical findings clearly, inequities in aid allocation, and the widespread outsourcing of statistics-related work. In exploring future applications, the article discusses the potential of impact-based early warning models, dynamic population data, and artificial intelligence to enhance communication and decision-making. Throughout, emphasis is placed on the need for interoperable systems as well as ethical and inclusive data practices. In doing so, the article presents statistics as both a diagnostic and strategic tool for strengthening the effectiveness, fairness, and responsiveness of humanitarian action in disaster contexts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.annualreviews.org/content/journals/10.1146/annurev-statistics-042424-061122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Science/arsia.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayesian spatiotemporal modelling of political violence and conflict events using discrete-time Hawkes processes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2026) Journal of Royal Statistical Society Series A: Statistics in Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immediately following a disaster event, such as an earthquake, estimates of the damage extent play a key role in informing the coordination of response and recovery efforts. We develop a novel impact estimation tool that leverages a generalised Bayesian approach to generate earthquake impact estimates across three impact types: mortality, population displacement, and building damage. Inference is performed within a likelihood-free framework, and a scoring-rule-based posterior avoids information loss from non-sufficient summary statistics. We propose an adaptation of existing scoring-rule-based loss functions that accommodates the use of an approximate Bayesian computation sequential Monte Carlo (ABC-SMC) framework. The fitted model achieves results comparable to those of two leading impact estimation tools in the prediction of total mortality when tested on a set of held-out past events. The proposed method provides four advantages over existing empirical approaches: modelling produces a gridded spatial map of the estimated impact, predictions benefit from the Bayesian quantification and interpretation of uncertainty, there is direct handling of multi-shock earthquake events, and the use of a joint model between impact types allows predictions to be updated as impact observations become available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2412.15791</t>
   </si>
   <si>
     <t xml:space="preserve">Images/Science/conflict.jpg</t>
@@ -227,12 +227,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -494,138 +498,138 @@
   <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
     </row>
